--- a/equipe/Alessandra_Ferreira.xlsx
+++ b/equipe/Alessandra_Ferreira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6834EF-72CB-4B83-88F3-9E3E795146F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7795F1B-93DD-4BBC-8E4A-C612F3BB152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E68C4C4A-A1A0-43B5-A958-5A1CD83B5C48}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t xml:space="preserve">Quarter </t>
   </si>
@@ -780,10 +780,10 @@
       <c r="M3" s="9">
         <v>0</v>
       </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3" s="11">
+      <c r="N3" s="9">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9">
         <v>0</v>
       </c>
       <c r="P3" s="5"/>
@@ -798,19 +798,45 @@
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
+      <c r="C4" s="5">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>24</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6">
+        <v>6</v>
+      </c>
+      <c r="H4" s="6">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8">
+        <v>4</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
       <c r="P4" s="5"/>
       <c r="R4" t="s">
         <v>35</v>
@@ -1019,7 +1045,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C2:D13" xr:uid="{C8C27F7A-79C7-4F9D-809C-AD6A6F393DA0}">
       <formula1>"1º,2º,3º,4º,5º,6º,7º,8º,9º,10º,11º,12º,13º,14º,15º,16º,17º,18º,19º,20º,21º,22º,23º,24º,25º,26º,27º,28º,29º,30º,31º,32º,33º,34º,35º,36º,37º,38º,39º,40º,Férias,Licença"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:M13" xr:uid="{3453BFE7-C6C3-4614-9C17-BDD6C0DE6B1A}">
+    <dataValidation type="list" allowBlank="1" sqref="K5:M13 K2:M2 K3:O4 J2:J13" xr:uid="{3453BFE7-C6C3-4614-9C17-BDD6C0DE6B1A}">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B13" xr:uid="{C6EF3457-5177-4CEB-94FA-7734A7FCDCE6}">

--- a/equipe/Alessandra_Ferreira.xlsx
+++ b/equipe/Alessandra_Ferreira.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dell-analytics-pro\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7795F1B-93DD-4BBC-8E4A-C612F3BB152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E146DC3E-C055-464B-832E-B0BB1A095BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E68C4C4A-A1A0-43B5-A958-5A1CD83B5C48}"/>
   </bookViews>
